--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_64_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_64_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
         <v>7</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>4</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3099,16 +3099,16 @@
         <v>32</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X26" t="n">
         <v>12</v>
@@ -3491,16 +3491,16 @@
         <v>9</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>4</v>
@@ -3827,16 +3827,16 @@
         <v>119</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X30" t="n">
         <v>29</v>
@@ -4292,16 +4292,16 @@
         <v>23</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X35" t="n">
         <v>5</v>
@@ -4684,10 +4684,10 @@
         <v>7</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>2</v>
@@ -5272,16 +5272,16 @@
         <v>2</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>1</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6252,16 +6252,16 @@
         <v>25</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>8</v>
@@ -6784,16 +6784,16 @@
         <v>95</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X48" t="n">
         <v>31</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_64_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_64_EL.xlsx
@@ -674,10 +674,10 @@
         <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="P2" t="n">
         <v>10</v>
@@ -695,17 +695,17 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
         <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>78.38</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>25.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1543,14 +1543,14 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
@@ -2374,11 +2374,11 @@
         <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -3111,14 +3111,14 @@
         <v>4</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
@@ -3158,11 +3158,11 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -3503,14 +3503,14 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y28" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" t="n">
-        <v>6</v>
-      </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>10</v>
       </c>
       <c r="X30" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="Y30" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,22 +3875,22 @@
         <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
         <v>8</v>
       </c>
       <c r="AK30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <v>2</v>
       </c>
       <c r="X35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y35" t="n">
         <v>5</v>
       </c>
-      <c r="Y35" t="n">
-        <v>8</v>
-      </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -4892,14 +4892,14 @@
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5872,10 +5872,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6460,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>5</v>
       </c>
       <c r="X48" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="Y48" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
